--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Assistenza domiciliare.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Assistenza domiciliare.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="107">
   <si>
     <r>
       <t xml:space="preserve">
@@ -159,7 +159,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Accedi allo sportello telematico</t>
+    <t>Richiedi assistenza</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -663,7 +663,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -671,8 +671,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> Trovi il testo completo nel piano assistenziale in allegato.
-Per consultare il piano assistenziale, [visita questo sito](URL).</t>
+      <t xml:space="preserve"> Trovi il testo completo nel piano assistenziale in allegato.</t>
     </r>
   </si>
   <si>
@@ -929,7 +928,7 @@
     <t>Disdici appuntamento</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Consulta il piano</t>
   </si>
   <si>
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
@@ -952,13 +951,16 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
       <t xml:space="preserve">
 File allegato al messaggio</t>
     </r>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>&lt;piano assistenziale&gt;</t>
@@ -1029,18 +1031,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -1800,82 +1790,82 @@
         <v>89</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D8" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="34" t="s">
-        <v>86</v>
-      </c>
       <c r="F8" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>57</v>
@@ -1884,19 +1874,19 @@
         <v>57</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="E11" s="34" t="s">
         <v>57</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
